--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,6 +1421,337 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122249639</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98149</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skyltaren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579773</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6653322</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122249629</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skyltaren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579862</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6653332</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122249638</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skyltaren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579762</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6653350</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249639</v>
+        <v>122249629</v>
       </c>
       <c r="B9" t="n">
-        <v>98149</v>
+        <v>92037</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,50 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579773</v>
+        <v>579862</v>
       </c>
       <c r="R9" t="n">
-        <v>6653322</v>
+        <v>6653332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1512,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1547,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249629</v>
+        <v>122249639</v>
       </c>
       <c r="B10" t="n">
-        <v>92030</v>
+        <v>98157</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,38 +1546,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579862</v>
+        <v>579773</v>
       </c>
       <c r="R10" t="n">
-        <v>6653332</v>
+        <v>6653322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,6 +1630,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +1754,135 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122273384</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98157</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skyltaren, 200 m OSO om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579774</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6653323</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>U-Sal-1136</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>proj. Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>122249629</v>
       </c>
       <c r="B9" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249639</v>
+        <v>122249638</v>
       </c>
       <c r="B10" t="n">
-        <v>98157</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,50 +1546,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579773</v>
+        <v>579762</v>
       </c>
       <c r="R10" t="n">
-        <v>6653322</v>
+        <v>6653350</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1618,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1653,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249638</v>
+        <v>122249639</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>98159</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,38 +1652,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579762</v>
+        <v>579773</v>
       </c>
       <c r="R11" t="n">
-        <v>6653350</v>
+        <v>6653322</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,6 +1736,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249629</v>
+        <v>122249639</v>
       </c>
       <c r="B9" t="n">
-        <v>92039</v>
+        <v>98159</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,38 +1440,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579862</v>
+        <v>579773</v>
       </c>
       <c r="R9" t="n">
-        <v>6653332</v>
+        <v>6653322</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,6 +1524,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1534,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249638</v>
+        <v>122249629</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>92039</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,21 +1563,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579762</v>
+        <v>579862</v>
       </c>
       <c r="R10" t="n">
-        <v>6653350</v>
+        <v>6653332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249639</v>
+        <v>122249638</v>
       </c>
       <c r="B11" t="n">
-        <v>98159</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,50 +1665,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579773</v>
+        <v>579762</v>
       </c>
       <c r="R11" t="n">
-        <v>6653322</v>
+        <v>6653350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1737,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249639</v>
+        <v>122249629</v>
       </c>
       <c r="B9" t="n">
-        <v>98159</v>
+        <v>92055</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,50 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579773</v>
+        <v>579862</v>
       </c>
       <c r="R9" t="n">
-        <v>6653322</v>
+        <v>6653332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1512,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1547,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249629</v>
+        <v>122249639</v>
       </c>
       <c r="B10" t="n">
-        <v>92039</v>
+        <v>98175</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,38 +1546,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579862</v>
+        <v>579773</v>
       </c>
       <c r="R10" t="n">
-        <v>6653332</v>
+        <v>6653322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,6 +1630,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98159</v>
+        <v>98175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249629</v>
+        <v>122249639</v>
       </c>
       <c r="B9" t="n">
-        <v>92055</v>
+        <v>98175</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,38 +1440,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579862</v>
+        <v>579773</v>
       </c>
       <c r="R9" t="n">
-        <v>6653332</v>
+        <v>6653322</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,6 +1524,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1534,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249639</v>
+        <v>122249638</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,50 +1559,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579773</v>
+        <v>579762</v>
       </c>
       <c r="R10" t="n">
-        <v>6653322</v>
+        <v>6653350</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1631,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249638</v>
+        <v>122249629</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>92055</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579762</v>
+        <v>579862</v>
       </c>
       <c r="R11" t="n">
-        <v>6653350</v>
+        <v>6653332</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>122249639</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249638</v>
+        <v>122249629</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>92065</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,21 +1563,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579762</v>
+        <v>579862</v>
       </c>
       <c r="R10" t="n">
-        <v>6653350</v>
+        <v>6653332</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249629</v>
+        <v>122249638</v>
       </c>
       <c r="B11" t="n">
-        <v>92055</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579862</v>
+        <v>579762</v>
       </c>
       <c r="R11" t="n">
-        <v>6653332</v>
+        <v>6653350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>122249639</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>122249629</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>122249639</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>122249629</v>
       </c>
       <c r="B10" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1431,7 +1431,7 @@
         <v>122249639</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,11 +1445,6 @@
       </c>
       <c r="E9" t="n">
         <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1550,7 +1545,7 @@
         <v>122249629</v>
       </c>
       <c r="B10" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,11 +1559,6 @@
       </c>
       <c r="E10" t="n">
         <v>4364</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1671,11 +1661,6 @@
       <c r="E11" t="n">
         <v>100526</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Callidium coriaceum</t>
@@ -1762,7 +1747,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,11 +1761,6 @@
       </c>
       <c r="E12" t="n">
         <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249639</v>
+        <v>122249638</v>
       </c>
       <c r="B9" t="n">
-        <v>98211</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,45 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579773</v>
+        <v>579762</v>
       </c>
       <c r="R9" t="n">
-        <v>6653322</v>
+        <v>6653350</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1512,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1545,7 +1537,7 @@
         <v>122249629</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,6 +1551,11 @@
       </c>
       <c r="E10" t="n">
         <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1643,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249638</v>
+        <v>122249639</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>98224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,33 +1652,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579762</v>
+        <v>579773</v>
       </c>
       <c r="R11" t="n">
-        <v>6653350</v>
+        <v>6653322</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,6 +1736,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1747,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,6 +1776,11 @@
       </c>
       <c r="E12" t="n">
         <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249638</v>
+        <v>122249639</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,38 +1440,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579762</v>
+        <v>579773</v>
       </c>
       <c r="R9" t="n">
-        <v>6653350</v>
+        <v>6653322</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,6 +1524,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1534,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249629</v>
+        <v>122249638</v>
       </c>
       <c r="B10" t="n">
-        <v>92100</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,21 +1563,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579862</v>
+        <v>579762</v>
       </c>
       <c r="R10" t="n">
-        <v>6653332</v>
+        <v>6653350</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249639</v>
+        <v>122249629</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>92113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,50 +1665,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579773</v>
+        <v>579862</v>
       </c>
       <c r="R11" t="n">
-        <v>6653322</v>
+        <v>6653332</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1737,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249639</v>
+        <v>122249629</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>92114</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,50 +1440,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579773</v>
+        <v>579862</v>
       </c>
       <c r="R9" t="n">
-        <v>6653322</v>
+        <v>6653332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1512,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1653,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249629</v>
+        <v>122249639</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,38 +1652,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579862</v>
+        <v>579773</v>
       </c>
       <c r="R11" t="n">
-        <v>6653332</v>
+        <v>6653322</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,6 +1736,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249629</v>
+        <v>122249638</v>
       </c>
       <c r="B9" t="n">
-        <v>92114</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579862</v>
+        <v>579762</v>
       </c>
       <c r="R9" t="n">
-        <v>6653332</v>
+        <v>6653350</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249638</v>
+        <v>122249639</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,38 +1546,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579762</v>
+        <v>579773</v>
       </c>
       <c r="R10" t="n">
-        <v>6653350</v>
+        <v>6653322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,6 +1630,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1640,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249639</v>
+        <v>122249629</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>92114</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,50 +1665,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579773</v>
+        <v>579862</v>
       </c>
       <c r="R11" t="n">
-        <v>6653322</v>
+        <v>6653332</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1737,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -1537,7 +1537,7 @@
         <v>122249639</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>122249629</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>122273384</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113270993</v>
+        <v>113271026</v>
       </c>
       <c r="B2" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580038</v>
+        <v>579704</v>
       </c>
       <c r="R2" t="n">
-        <v>6653380</v>
+        <v>6653306</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,8 +754,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271026</v>
+        <v>122249638</v>
       </c>
       <c r="B3" t="n">
-        <v>79469</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2080</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsjön, Vstm</t>
+          <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579704</v>
+        <v>579762</v>
       </c>
       <c r="R3" t="n">
-        <v>6653306</v>
+        <v>6653350</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,14 +861,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -893,53 +883,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113271133</v>
+        <v>122249639</v>
       </c>
       <c r="B4" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergsjön, Vstm</t>
+          <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579999</v>
+        <v>579773</v>
       </c>
       <c r="R4" t="n">
-        <v>6653389</v>
+        <v>6653322</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,53 +997,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271136</v>
+        <v>122273384</v>
       </c>
       <c r="B5" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergsjön, Vstm</t>
+          <t>Skyltaren, 200 m OSO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580021</v>
+        <v>579774</v>
       </c>
       <c r="R5" t="n">
-        <v>6653370</v>
+        <v>6653323</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,14 +1072,24 @@
           <t>Västerfärnebo</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>U-Sal-1136</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>proj. Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,13 +1098,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1099,21 +1115,16 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113270994</v>
+        <v>113270996</v>
       </c>
       <c r="B6" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,21 +1132,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>73</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579935</v>
+        <v>579978</v>
       </c>
       <c r="R6" t="n">
-        <v>6653406</v>
+        <v>6653418</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,6 +1202,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1211,37 +1227,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270996</v>
+        <v>113271136</v>
       </c>
       <c r="B7" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579978</v>
+        <v>580021</v>
       </c>
       <c r="R7" t="n">
-        <v>6653418</v>
+        <v>6653370</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1297,11 +1308,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>asplåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1322,15 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271154</v>
+        <v>122249629</v>
       </c>
       <c r="B8" t="n">
-        <v>5015</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,37 +1339,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101608</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergsjön, Vstm</t>
+          <t>Skyltaren, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579815</v>
+        <v>579862</v>
       </c>
       <c r="R8" t="n">
-        <v>6653363</v>
+        <v>6653332</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,12 +1393,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,53 +1429,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122249638</v>
+        <v>113270993</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skyltaren, Vstm</t>
+          <t>Bergsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579762</v>
+        <v>580038</v>
       </c>
       <c r="R9" t="n">
-        <v>6653350</v>
+        <v>6653380</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,12 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,65 +1530,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122249639</v>
+        <v>113270994</v>
       </c>
       <c r="B10" t="n">
-        <v>98241</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skyltaren, Vstm</t>
+          <t>Bergsjön, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579773</v>
+        <v>579935</v>
       </c>
       <c r="R10" t="n">
-        <v>6653322</v>
+        <v>6653406</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,12 +1595,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,7 +1609,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1653,15 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122249629</v>
+        <v>113271133</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,37 +1642,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skyltaren, Vstm</t>
+          <t>Bergsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579862</v>
+        <v>579999</v>
       </c>
       <c r="R11" t="n">
-        <v>6653332</v>
+        <v>6653389</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,12 +1696,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,135 +1727,6 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>122273384</v>
-      </c>
-      <c r="B12" t="n">
-        <v>98241</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Skyltaren, 200 m OSO om (knärot), Vstm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>579774</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6653323</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Sala</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Västerfärnebo</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>U-Sal-1136</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>proj. Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Bo Eriksson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 40495-2024 artfynd.xlsx
+++ b/artfynd/A 40495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113270996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271136</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122249629</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113270993</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113270994</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113271133</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122249638</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122249639</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,8 +1779,25 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122273384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>